--- a/data/credit_bond_all_2026-10-15.xlsx
+++ b/data/credit_bond_all_2026-10-15.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ115"/>
+  <dimension ref="A1:AZ118"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -741,7 +741,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -931,7 +931,9 @@
       <c r="E4" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>4.7</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -1129,7 +1131,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1155,7 +1159,9 @@
       <c r="E5" s="4" t="n">
         <v>4.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.00</t>
@@ -1185,7 +1191,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5700/1.5200</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1385,7 +1391,9 @@
       <c r="E6" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>2.20 ~ 3.20</t>
@@ -1451,7 +1459,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>2.05%~2.15%</t>
+        </is>
+      </c>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
@@ -1567,7 +1579,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -1593,7 +1607,9 @@
       <c r="E7" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>5.8</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.10</t>
@@ -2305,7 +2321,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/1.5500</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2345,7 +2361,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2521,7 +2541,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>1.5800/1.5400</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2561,7 +2581,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.54%~1.64%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2926,7 +2950,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>012682448.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>0.73Y</t>
@@ -2965,7 +2993,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4600</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -3005,7 +3033,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3142,7 +3174,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102684033.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -3181,7 +3217,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8100/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3221,7 +3257,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3360,7 +3400,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>012682450.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>0.21Y</t>
@@ -3399,7 +3443,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4700/1.4500</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3439,7 +3483,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.43%~1.47%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3576,7 +3624,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>012682446.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -3615,7 +3667,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3655,7 +3707,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3792,7 +3848,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>102684029.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -3831,7 +3891,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9350/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -3871,7 +3931,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.86%~1.96%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4008,7 +4072,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>102684039.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -4087,7 +4155,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>2.04%~2.14%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4215,7 +4287,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
@@ -4267,7 +4341,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4452,7 +4526,11 @@
           <t>10-16 18:00</t>
         </is>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>102684055.IB</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4531,7 +4609,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X20" s="3"/>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4655,7 +4737,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
@@ -4668,7 +4752,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>012682449.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>0.25Y</t>
@@ -4747,7 +4835,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X21" s="3"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>2.16%~2.20%</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4884,7 +4976,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>042680342.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -4963,7 +5059,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.93%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -5091,7 +5191,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -5104,7 +5206,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>102684035.IB</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -5143,7 +5249,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5183,7 +5289,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5308,7 +5418,7 @@
         </is>
       </c>
       <c r="AZ23" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
@@ -5322,7 +5432,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>042680343.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -5361,7 +5475,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5401,7 +5515,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X24" s="3"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.44%~1.48%</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5542,7 +5660,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>102684045.IB</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -5581,7 +5703,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/1.6800</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5621,7 +5743,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5758,7 +5884,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>102684036.IB</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -5797,7 +5927,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -5837,7 +5967,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5965,7 +6099,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
@@ -5978,7 +6114,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>102684037.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -6017,7 +6157,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6057,7 +6197,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X27" s="3"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6185,7 +6329,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ27" s="3"/>
+      <c r="AZ27" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -6198,7 +6344,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>102690067.IB</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -6237,7 +6387,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5100</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -6277,7 +6427,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X28" s="3"/>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.66%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6414,7 +6568,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>102684049.IB</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -6453,7 +6611,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -6493,7 +6651,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X29" s="3"/>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6612,7 +6774,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26华能山东SCP003</t>
+          <t>26津城建MTN019</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6620,10 +6782,14 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>102684034.IB</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -6632,44 +6798,44 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.60</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25华能山东MTN001</t>
+          <t>25津投08</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.02Y</t>
+          <t>4.10Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6024</t>
+          <t>1.7939</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>华能山东发电有限公司</t>
+          <t>天津城市基础设施建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C+ 34.13</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6679,7 +6845,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-15 14:00</t>
+          <t>10-15 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6699,37 +6865,45 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X30" s="3"/>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z30" s="3"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额为0亿元,发行金额上限为10亿元,拟将全部募集资金用于偿还发行人及其下属子公司有息债务。</t>
+          <t>本期中期票据发行规模10亿元。募集资金全部用于偿还天津城市基础设施建设投资集团有限公司本部债务融资工具本金。[24津城建MTN006,23津城建MTN015]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -6739,7 +6913,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>华能山东发电有限公司2026年度第三期超短期融资券</t>
+          <t>天津城市基础设施建设投资集团有限公司2026年度第十九期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6749,7 +6923,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2030-10-16</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -6770,32 +6944,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6828,7 +7002,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26津城建MTN019</t>
+          <t>26中铁工业MTN001(科创债)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6836,41 +7010,45 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C31" s="3"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>102684052.IB</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25津投08</t>
+          <t>25中铁工业MTN001(科创债)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.10Y</t>
+          <t>4.08Y+N</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7939</t>
+          <t>1.7687</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -6880,12 +7058,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>天津城市基础设施建设投资集团有限公司</t>
+          <t>中铁高新工业股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.13</t>
+          <t>D 4.96</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6895,7 +7073,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-15 09:00</t>
+          <t>10-15 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -6912,10 +7090,14 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X31" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>1.77%~1.87%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6928,17 +7110,17 @@
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元。募集资金全部用于偿还天津城市基础设施建设投资集团有限公司本部债务融资工具本金。[24津城建MTN006,23津城建MTN015]</t>
+          <t>本期中期票据发行规模上限为12亿元,基础发行规模为0亿元,全部用于偿还发行人有息债务。[工业YK04,24中铁工业MTN001A(科创票据)]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,平安银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -6949,7 +7131,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -6959,7 +7141,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>天津城市基础设施建设投资集团有限公司2026年度第十九期中期票据</t>
+          <t>中铁高新工业股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -6969,7 +7151,7 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2030-10-16</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -6990,7 +7172,7 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
@@ -7000,22 +7182,22 @@
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>工程设备</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>工程设备</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>运输设备</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7030,12 +7212,12 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY31" s="3" t="inlineStr">
@@ -7048,7 +7230,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26中铁工业MTN001(科创债)</t>
+          <t>26山高建管MTN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7056,56 +7238,60 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>102684023.IB</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 1.90</t>
         </is>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25中铁工业MTN001(科创债)</t>
+          <t>25山高建管MTN001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.08Y+N</t>
+          <t>2.17Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7687</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/1.6500</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>中铁高新工业股份有限公司</t>
+          <t>山东高速建设管理集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>D 4.96</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7115,7 +7301,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-15 15:00</t>
+          <t>10-15 10:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7132,33 +7318,33 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X32" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模上限为12亿元,基础发行规模为0亿元,全部用于偿还发行人有息债务。[工业YK04,24中铁工业MTN001A(科创票据)]</t>
+          <t>本期中期票据拟发行金额5亿元,所募集的资金拟全部用于偿还发行人及子公司到期有息负债。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7169,7 +7355,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7179,7 +7365,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>中铁高新工业股份有限公司2026年度第一期科技创新债券</t>
+          <t>山东高速建设管理集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7210,32 +7396,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>工程设备</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>工程设备</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>运输设备</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7250,12 +7436,12 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7263,12 +7449,14 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26山高建管MTN001</t>
+          <t>26宁紫01</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7276,51 +7464,55 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C33" s="3"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>246217.SH</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 1.90</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25山高建管MTN001</t>
+          <t>26湘江资产MTN001</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.17Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.9384</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>1.9400/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>山东高速建设管理集团有限公司</t>
+          <t>南京紫金资产管理有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -7335,7 +7527,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>10-15 10:00</t>
+          <t>10-15 16:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7345,42 +7537,50 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行金额5亿元,所募集的资金拟全部用于偿还发行人及子公司到期有息负债。</t>
+          <t>本期公司债券募集资金扣除发行费用后拟全部用于偿还有息债务,其中偿还公司债券本金10亿元,偿还公司债券利息、银行借款2亿元[21宁紫01]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>南京紫金投资集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7390,12 +7590,12 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>山东高速建设管理集团有限公司2026年度第一期中期票据</t>
+          <t>南京紫金资产管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7405,53 +7605,57 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7461,7 +7665,7 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
@@ -7484,7 +7688,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26宁紫01</t>
+          <t>26财融G6</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7494,43 +7698,43 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>246217.SH</t>
+          <t>246235.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26湘江资产MTN001</t>
+          <t>24财通租赁MTN003</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.9384</t>
+          <t>1.7701</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7540,12 +7744,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>南京紫金资产管理有限公司</t>
+          <t>无锡财通融资租赁有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 19.24</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7572,36 +7776,36 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后拟全部用于偿还有息债务,其中偿还公司债券本金10亿元,偿还公司债券利息、银行借款2亿元[21宁紫01]</t>
+          <t>本期债券募集资金不超过人民币10亿元(含人民币10亿元),扣除发行费用后,拟全部用于偿还回售公司债券本金[23财通G4]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>南京紫金投资集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7619,7 +7823,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>南京紫金资产管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>无锡财通融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7629,14 +7833,10 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-19</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7669,12 +7869,12 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
@@ -7689,7 +7889,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -7712,7 +7912,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26财融G6</t>
+          <t>26深圳资产MTN001B</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7722,43 +7922,43 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>246235.SH</t>
+          <t>102684025.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24财通租赁MTN003</t>
+          <t>25深圳资产MTN001</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>3.76Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.7701</t>
+          <t>1.9420</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -7768,12 +7968,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>无锡财通融资租赁有限公司</t>
+          <t>深圳资产管理有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 19.24</t>
+          <t>C- 21.09</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7783,7 +7983,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-15 16:00</t>
+          <t>10-15 09:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7793,17 +7993,21 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7812,23 +8016,23 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过人民币10亿元(含人民币10亿元),扣除发行费用后,拟全部用于偿还回售公司债券本金[23财通G4]</t>
+          <t>本期中期票据采取发行金额动态调整机制,基础发行规模为0亿元,发行规模上限为5亿元(含5亿元),发行人拟将本期中期票据募集资金全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -7838,12 +8042,12 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>无锡财通融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
+          <t>深圳资产管理有限公司2026年度第一期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7853,13 +8057,13 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
@@ -7869,7 +8073,7 @@
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
@@ -7879,7 +8083,7 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
@@ -7889,12 +8093,12 @@
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
@@ -7932,7 +8136,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26深圳资产MTN001B</t>
+          <t>26黔高05</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7940,56 +8144,60 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C36" s="3"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>246240.SH</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>25深圳资产MTN001</t>
+          <t>26贵州高速MTN004</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>3.76Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.9420</t>
+          <t>1.6495</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/1.6200</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>深圳资产管理有限公司</t>
+          <t>贵州高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 21.09</t>
+          <t>C+ 34.01</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -7999,7 +8207,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-15 09:00</t>
+          <t>10-15 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8009,17 +8217,21 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8028,23 +8240,23 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据采取发行金额动态调整机制,基础发行规模为0亿元,发行规模上限为5亿元(含5亿元),发行人拟将本期中期票据募集资金全部用于偿还有息负债</t>
+          <t>本期债券募集资金20.00亿元拟用于偿还到期公司债券本金[23黔高03]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8054,12 +8266,12 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>深圳资产管理有限公司2026年度第一期中期票据(品种二)</t>
+          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8069,53 +8281,53 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8148,7 +8360,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26黔高05</t>
+          <t>建材YK26</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8158,12 +8370,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>246240.SH</t>
+          <t>246222.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -8172,44 +8384,44 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26贵州高速MTN004</t>
+          <t>建材YK24</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>4.98Y+N</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6495</t>
+          <t>1.7144</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/1.6990</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司</t>
+          <t>中国建材股份有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.01</t>
+          <t>B- 46.38</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8219,7 +8431,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>10-15 15:00</t>
+          <t>10-15 16:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8236,10 +8448,14 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X37" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8248,17 +8464,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金20.00亿元拟用于偿还到期公司债券本金[23黔高03]</t>
+          <t>本期债券募集资金扣除发行等相关费用后，拟用于生产性支出，包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8269,7 +8485,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8279,7 +8495,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种一)</t>
+          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8289,10 +8505,14 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8310,32 +8530,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8350,7 +8570,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8368,7 +8588,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>建材YK26</t>
+          <t>26亦庄K7</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8378,58 +8598,58 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>246222.SH</t>
+          <t>246201.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>10.0</v>
+        <v>7.5</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>建材YK24</t>
+          <t>26亦庄K5</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.98Y+N</t>
+          <t>9.84Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.7144</t>
+          <t>1.9620</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.7200/1.7100</t>
+          <t>1.9600/1.8500</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司</t>
+          <t>北京亦庄国际投资发展有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 46.38</t>
+          <t>C- 14.18</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8456,10 +8676,14 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X38" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.94%~2.04%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8473,12 +8697,12 @@
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后，拟用于生产性支出，包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于科技创新相关的权益出资。发行人前期如有自筹资金预先投入,本期债券可以置换前期自筹资金。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,第一创业证券承销保荐有限责任公司,平安证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8489,7 +8713,7 @@
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -8499,7 +8723,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
+          <t>北京亦庄国际投资发展有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8509,7 +8733,7 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
+          <t>2036-10-19</t>
         </is>
       </c>
       <c r="AK38" s="3" t="inlineStr">
@@ -8539,27 +8763,27 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8574,7 +8798,7 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
@@ -8592,7 +8816,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26亦庄K7</t>
+          <t>26亦庄K6</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8602,12 +8826,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>246201.SH</t>
+          <t>246200.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -8616,34 +8840,34 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26亦庄K5</t>
+          <t>26亦庄K3</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>9.84Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.9620</t>
+          <t>1.6550</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.6300</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -8683,7 +8907,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X39" s="3"/>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8723,7 +8951,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>北京亦庄国际投资发展有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)(品种二)</t>
+          <t>北京亦庄国际投资发展有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8733,7 +8961,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2036-10-19</t>
+          <t>2031-10-19</t>
         </is>
       </c>
       <c r="AK39" s="3" t="inlineStr">
@@ -8816,7 +9044,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26亦庄K6</t>
+          <t>26投控Z2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8826,58 +9054,58 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>246200.SH</t>
+          <t>520525.SZ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26亦庄K3</t>
+          <t>26投控K1</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.6550</t>
+          <t>1.9252</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>北京亦庄国际投资发展有限公司</t>
+          <t>青岛海控投资控股有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 14.18</t>
+          <t>C- 14.58</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8887,7 +9115,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10-15 16:00</t>
+          <t>10-15 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -8904,10 +9132,14 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X40" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.99%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8916,17 +9148,17 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于科技创新相关的权益出资。发行人前期如有自筹资金预先投入,本期债券可以置换前期自筹资金。</t>
+          <t>本期债券发行总额不超过5亿元,本期债券募集资金全部用于通过支付预付款或者清偿应付款项等形式支持产业链上下游或与自身经营业务相关的中小微企业发展</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,第一创业证券承销保荐有限责任公司,平安证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -8942,29 +9174,25 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>北京亦庄国际投资发展有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)(品种一)</t>
+          <t>青岛海控投资控股有限公司2026年面向专业投资者非公开发行中小微企业支持债券(第二期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-19</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8987,7 +9215,7 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
@@ -9007,7 +9235,7 @@
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高低压设备</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9040,7 +9268,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26投控Z2</t>
+          <t>26泰山05</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9050,16 +9278,16 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>520525.SZ</t>
+          <t>284188.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
@@ -9071,37 +9299,37 @@
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26投控K1</t>
+          <t>26泰山03</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.9252</t>
+          <t>2.0146</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0000/1.9000</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>青岛海控投资控股有限公司</t>
+          <t>泰安市泰山财金投资集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 14.58</t>
+          <t>C- 21.22</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9121,36 +9349,40 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X41" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>2.02%~2.12%</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>山东省-泰安市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过5亿元,本期债券募集资金全部用于通过支付预付款或者清偿应付款项等形式支持产业链上下游或与自身经营业务相关的中小微企业发展</t>
+          <t>本期债券拟募集资金规模不超过20亿元,债券募集资金扣除发行费用后拟全部用于偿还公司债券回售本金。[23泰山01]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,中泰证券股份有限公司,德邦证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9166,12 +9398,12 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>青岛海控投资控股有限公司2026年面向专业投资者非公开发行中小微企业支持债券(第二期)</t>
+          <t>泰安市泰山财金投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9181,7 +9413,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9197,7 +9429,7 @@
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
@@ -9207,7 +9439,7 @@
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
@@ -9217,17 +9449,17 @@
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>高低压设备</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9260,7 +9492,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26泰山05</t>
+          <t>26华鑫K1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9270,58 +9502,58 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>284188.SH</t>
+          <t>284153.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1.01Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.00 ~ 2.00</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26泰山03</t>
+          <t>26华鑫01</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>1.31Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.0146</t>
+          <t>1.5592</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>泰安市泰山财金投资集团有限公司</t>
+          <t>华鑫证券有限责任公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 21.22</t>
+          <t>C+ 30.66</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9341,17 +9573,21 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X42" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.61%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9360,23 +9596,23 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>山东省-泰安市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金规模不超过20亿元,债券募集资金扣除发行费用后拟全部用于偿还公司债券回售本金。[23泰山01]</t>
+          <t>本期债券募集资金规模不超过3.00亿元(含3.00亿元),在扣除发行费用后,拟将不低于70%募集资金用于科技创新领域,剩余不超过30%募集资金用于补充公司营运资金或偿还公司债务等法律法规允许的用途。</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,中泰证券股份有限公司,德邦证券股份有限公司,财达证券股份有限公司</t>
+          <t>华鑫证券有限责任公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9391,7 +9627,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>泰安市泰山财金投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>华鑫证券有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9401,7 +9637,7 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2027-10-21</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
@@ -9417,37 +9653,37 @@
       </c>
       <c r="AN42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9480,7 +9716,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26华鑫K1</t>
+          <t>26迈瑞03</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9490,58 +9726,58 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>284153.SH</t>
+          <t>284260.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>1.01Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.00 ~ 2.00</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26华鑫01</t>
+          <t>26迈瑞02</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>1.31Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.5592</t>
+          <t>1.7890</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/1.7600</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>华鑫证券有限责任公司</t>
+          <t>重庆迈瑞城市建设投资有限责任公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.66</t>
+          <t>C+ 31.18</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9561,17 +9797,21 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X43" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9580,23 +9820,23 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>重庆市-沙坪坝区</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金规模不超过3.00亿元(含3.00亿元),在扣除发行费用后,拟将不低于70%募集资金用于科技创新领域,剩余不超过30%募集资金用于补充公司营运资金或偿还公司债务等法律法规允许的用途。</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金[25迈瑞D4,25迈瑞D5]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>华鑫证券有限责任公司</t>
+          <t>国投证券股份有限公司,国泰海通证券股份有限公司,西南证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -9611,7 +9851,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>华鑫证券有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>重庆迈瑞城市建设投资有限责任公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9621,7 +9861,7 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2027-10-21</t>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
@@ -9637,37 +9877,37 @@
       </c>
       <c r="AN43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -9700,7 +9940,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26迈瑞03</t>
+          <t>26自高01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9710,58 +9950,58 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>284260.SH</t>
+          <t>284233.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>13.0</v>
+        <v>7.5</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.00 ~ 3.20</t>
         </is>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26迈瑞02</t>
+          <t>24自高01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>109D</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.7890</t>
+          <t>1.8483</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8800/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>重庆迈瑞城市建设投资有限责任公司</t>
+          <t>自贡高新国有资本投资运营集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.18</t>
+          <t>C 25.94</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -9788,29 +10028,33 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X44" s="3"/>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>2.28%~2.38%</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>重庆市-沙坪坝区</t>
+          <t>四川省-自贡市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金[25迈瑞D4,25迈瑞D5]</t>
+          <t>本期债券的发行总额不超过7.50亿元(含7.50亿元)。本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金。[23自高01]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,国泰海通证券股份有限公司,西南证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -9831,7 +10075,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>重庆迈瑞城市建设投资有限责任公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>自贡高新国有资本投资运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -9841,7 +10085,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2029-10-16</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
@@ -9862,29 +10106,17 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3"/>
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="3"/>
       <c r="AT44" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -9920,17 +10152,17 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26自高01</t>
+          <t>26仪征03</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>10-15 18:00</t>
+          <t>10-15 17:30</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>284233.SH</t>
+          <t>284267.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -9939,34 +10171,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>24自高01</t>
+          <t>26仪征01</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>109D</t>
+          <t>4.22Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.8483</t>
+          <t>1.8186</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -9976,12 +10208,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>自贡高新国有资本投资运营集团有限公司</t>
+          <t>仪征市城市发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 25.94</t>
+          <t>C- 13.39</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10008,29 +10240,33 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X45" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.90%~2.00%</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>四川省-自贡市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券的发行总额不超过7.50亿元(含7.50亿元)。本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金。[23自高01]</t>
+          <t>本期债券募集资金5.00亿元拟用于偿还到期公司债券本金[23仪征03]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>东吴证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -10051,7 +10287,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>自贡高新国有资本投资运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>仪征市城市发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10087,12 +10323,24 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ45" s="3"/>
-      <c r="AR45" s="3"/>
-      <c r="AS45" s="3"/>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -10128,17 +10376,17 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26仪征03</t>
+          <t>26桐控06</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>10-15 17:30</t>
+          <t>10-15 17:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>284267.SH</t>
+          <t>284235.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -10147,49 +10395,49 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>5.0</v>
+        <v>7.02</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26仪征01</t>
+          <t>26桐控05</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>4.22Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.8186</t>
+          <t>1.8790</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9400/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>仪征市城市发展投资控股集团有限公司</t>
+          <t>桐庐县国有资本投资运营控股集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 13.39</t>
+          <t>C- 14.69</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10219,7 +10467,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X46" s="3"/>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>1.95%~2.05%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10228,17 +10480,17 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5.00亿元拟用于偿还到期公司债券本金[23仪征03]</t>
+          <t>本期公司债券募集资金扣除发行费用后,将全部仅用于偿还到期的公司债券“23桐旅03”本金。[23桐旅03]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>浙商证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
@@ -10259,7 +10511,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>仪征市城市发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>桐庐县国有资本投资运营控股集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10290,7 +10542,7 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
@@ -10315,7 +10567,7 @@
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10348,68 +10600,68 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26桐控06</t>
+          <t>26锦龙Y2</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>10-15 17:00</t>
+          <t>10-15 18:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>284235.SH</t>
+          <t>284187.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>7.02</v>
+        <v>6.8</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26桐控05</t>
+          <t>26锦龙GTY1</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>2.40Y+N</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.8790</t>
+          <t>2.0567</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9600</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>桐庐县国有资本投资运营控股集团有限公司</t>
+          <t>新疆锦龙电力集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 14.69</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10429,39 +10681,47 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X47" s="3"/>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>2.31%~2.41%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,将全部仅用于偿还到期的公司债券“23桐旅03”本金。[23桐旅03]</t>
+          <t>本次债券发行总额不超过6.80亿元,募集资金扣除发行费用后拟全部用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,东方证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD47" s="3"/>
+          <t>恒泰长财证券有限责任公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr">
+        <is>
+          <t>中新建电力集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE47" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10479,7 +10739,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>桐庐县国有资本投资运营控股集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
+          <t>新疆锦龙电力集团有限公司2026年面向专业投资者非公开发行可续期公司债券</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10489,7 +10749,7 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
@@ -10505,37 +10765,37 @@
       </c>
       <c r="AN47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10545,12 +10805,12 @@
       </c>
       <c r="AV47" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -10568,7 +10828,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26安建Y1</t>
+          <t>26江宁科学PPN001</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10576,45 +10836,41 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>246203.SH</t>
-        </is>
-      </c>
+      <c r="C48" s="3"/>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.20</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>25建工建投MTN001</t>
+          <t>25江宁科学PPN002</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.06Y</t>
+          <t>1.79Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2.2961</t>
+          <t>1.6379</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -10624,12 +10880,12 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>安徽建工建设投资集团有限公司</t>
+          <t>南京江宁科学园发展集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>C- 12.17</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10639,7 +10895,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>10-15 16:00</t>
+          <t>10-15 10:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -10649,17 +10905,21 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X48" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10668,23 +10928,23 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后拟全部用于偿还有息债务</t>
+          <t>本期拟发行2.00亿元,拟全部用于偿还发行人有息债务本金[26江宁科学SCP011]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -10694,75 +10954,75 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>安徽建工建设投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>南京江宁科学园发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM48" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AO48" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ48" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR48" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>市政路桥</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10770,7 +11030,7 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
@@ -10783,12 +11043,14 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ48" s="3"/>
+      <c r="AZ48" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26锦龙Y2</t>
+          <t>26衡阳水投PPN001</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10796,60 +11058,56 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>284187.SH</t>
-        </is>
-      </c>
+      <c r="C49" s="3"/>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+2+2+1</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>6.8</v>
+        <v>5.0</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26锦龙GTY1</t>
+          <t>24衡阳水投PPN001</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2.40Y+N</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>2.0567</t>
+          <t>1.8339</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>新疆锦龙电力集团有限公司</t>
+          <t>衡阳市湘江水利投资开发有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C- 15.79</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -10869,17 +11127,21 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X49" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>2.14%~2.24%</t>
+        </is>
+      </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -10888,27 +11150,23 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>湖南省-衡阳市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>本次债券发行总额不超过6.80亿元,募集资金扣除发行费用后拟全部用于偿还发行人有息债务</t>
+          <t>本期基础发行规模为人民币0亿元,本期发行金额上限为人民币5亿元,募集资金拟全部用于偿还存量债务融资工具[23湘江水利PPN001]</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>恒泰长财证券有限责任公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD49" s="3" t="inlineStr">
-        <is>
-          <t>中新建电力集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,长江证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
@@ -10918,12 +11176,12 @@
       </c>
       <c r="AG49" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>新疆锦龙电力集团有限公司2026年面向专业投资者非公开发行可续期公司债券</t>
+          <t>衡阳市湘江水利投资开发有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -10933,13 +11191,13 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2036-10-16</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
@@ -10949,52 +11207,52 @@
       </c>
       <c r="AN49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AV49" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW49" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX49" s="3" t="inlineStr">
@@ -11012,7 +11270,7 @@
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26江宁科学PPN001</t>
+          <t>26临沂投资PPN002</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -11023,53 +11281,53 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>25江宁科学PPN002</t>
+          <t>26临沂投资PPN001</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1.79Y</t>
+          <t>4.86Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.6379</t>
+          <t>2.1275</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0000</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>南京江宁科学园发展集团有限公司</t>
+          <t>临沂投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C- 12.17</t>
+          <t>C 26.37</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11079,7 +11337,7 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>10-15 10:00</t>
+          <t>10-15 14:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -11096,10 +11354,14 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X50" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>2.10%~2.20%</t>
+        </is>
+      </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -11108,17 +11370,17 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>山东省-临沂市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期拟发行2.00亿元,拟全部用于偿还发行人有息债务本金[26江宁科学SCP011]</t>
+          <t>发行人本期债务融资工具基础发行规模为0.00亿元,发行金额上限为12.00亿元,拟全部用于偿还债务融资工具本金[23临沂投资MTN002(可持续挂钩)]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>长城证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司,申万宏源证券有限公司,青岛银行股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
@@ -11139,7 +11401,7 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>南京江宁科学园发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>临沂投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11149,7 +11411,7 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2029-10-16</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK50" s="3"/>
@@ -11170,32 +11432,32 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11223,12 +11485,14 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ50" s="3"/>
+      <c r="AZ50" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26衡阳水投PPN001</t>
+          <t>26南翼01</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11236,56 +11500,60 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C51" s="3"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>284305.SH</t>
+        </is>
+      </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>5+2+2+1</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>24衡阳水投PPN001</t>
+          <t>25南翼02</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>3.84Y+5.00Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.8339</t>
+          <t>1.7669</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0800/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>衡阳市湘江水利投资开发有限公司</t>
+          <t>泉州市南翼投资集团有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C- 15.79</t>
+          <t>C- 19.14</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11295,7 +11563,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>10-15 15:00</t>
+          <t>10-15 16:00</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -11312,35 +11580,39 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X51" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>湖南省-衡阳市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行规模为人民币0亿元,本期发行金额上限为人民币5亿元,募集资金拟全部用于偿还存量债务融资工具[23湘江水利PPN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金或置换已用于偿还到期公司债券本金的自有资金[25南翼D1]</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,长江证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
@@ -11350,12 +11622,12 @@
       </c>
       <c r="AG51" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>衡阳市湘江水利投资开发有限公司2026年度第一期定向债务融资工具</t>
+          <t>泉州市南翼投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11365,13 +11637,17 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2036-10-16</t>
-        </is>
-      </c>
-      <c r="AK51" s="3"/>
+          <t>2033-10-16</t>
+        </is>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AM51" s="3" t="inlineStr">
@@ -11386,7 +11662,7 @@
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP51" s="3" t="inlineStr">
@@ -11444,7 +11720,7 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26临沂投资PPN002</t>
+          <t>26常熟经开PPN001</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -11459,49 +11735,49 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26临沂投资PPN001</t>
+          <t>26常经01</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>4.86Y</t>
+          <t>4.82Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2.1275</t>
+          <t>1.8382</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8500/1.7700</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>临沂投资发展集团有限公司</t>
+          <t>常熟经开控股有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C 26.37</t>
+          <t>B- 44.89</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -11511,7 +11787,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>10-15 14:00</t>
+          <t>10-15 09:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -11528,29 +11804,33 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X52" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>1.86%~1.96%</t>
+        </is>
+      </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>山东省-临沂市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具基础发行规模为0.00亿元,发行金额上限为12.00亿元,拟全部用于偿还债务融资工具本金[23临沂投资MTN002(可持续挂钩)]</t>
+          <t>发行人本次发行定向工具5亿元,本期债务融资工具募集资金拟用于偿还接续“23常熟经开PPN001”的专项过桥贷款[23常熟经开PPN001]</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司,申万宏源证券有限公司,青岛银行股份有限公司,广发证券股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司,中国光大银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
@@ -11571,7 +11851,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>临沂投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>常熟经开控股有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -11602,7 +11882,7 @@
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
@@ -11612,22 +11892,22 @@
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
-        </is>
-      </c>
-      <c r="AR52" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -11660,49 +11940,43 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26仁怀酱酒PPN002</t>
+          <t>华纬转债</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>10-15 18:00</t>
-        </is>
-      </c>
-      <c r="C53" s="3"/>
+          <t>10-15 15:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>127118.SZ</t>
+        </is>
+      </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.0</v>
+        <v>5.75</v>
       </c>
       <c r="F53" s="3"/>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>3.50 ~ 4.00</t>
-        </is>
-      </c>
-      <c r="H53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="4" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>25仁怀酱酒PPN002</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>4.08Y+5.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>3.1266</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -11712,14 +11986,10 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>仁怀酱酒(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
+          <t>华纬科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P53" s="3"/>
       <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -11727,7 +11997,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>10-15 09:00</t>
+          <t>10-15 09:15</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -11737,14 +12007,14 @@
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X53" s="3"/>
@@ -11753,102 +12023,102 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="Z53" s="3"/>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>贵州省-遵义市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额1.00亿元,募集资金扣除发行费用后,用于归还发行人到期债务融资工具[25仁怀酱酒PPN001(乡村振兴)]</t>
+          <t>公司本次向不特定对象发行可转换公司债券募集资金总额不超过57,500.00万元(含本数),扣除发行费用后将全部用于以下项目:</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>贵阳银行股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>仁怀酱酒(集团)有限责任公司2026年度第二期定向债务融资工具</t>
+          <t>2026年华纬科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2036-10-16</t>
+          <t>2032-10-15</t>
         </is>
       </c>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AM53" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP53" s="3"/>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>交运设备制造</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>道路运输设备</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>零部件</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>饮料制造</t>
+          <t>汽车零部件</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t/>
         </is>
       </c>
       <c r="AV53" s="3" t="inlineStr">
@@ -11858,7 +12128,7 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -11876,7 +12146,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26南翼01</t>
+          <t>G风电K1</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -11886,58 +12156,58 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>284305.SH</t>
+          <t>246218.SH</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>25南翼02</t>
+          <t>25风电K2</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>3.84Y+5.00Y</t>
+          <t>3.56Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.7669</t>
+          <t>1.7091</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>泉州市南翼投资集团有限公司</t>
+          <t>中节能风力发电股份有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C- 19.14</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -11957,36 +12227,36 @@
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金或置换已用于偿还到期公司债券本金的自有资金[25南翼D1]</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟用于置换12个月内绿色项目相关的自有资金支出。</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -11997,7 +12267,7 @@
       </c>
       <c r="AF54" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG54" s="3" t="inlineStr">
@@ -12007,17 +12277,17 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>泉州市南翼投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中节能风力发电股份有限公司2026年面向专业投资者公开发行绿色科技创新公司债券(气候主题)(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2033-10-16</t>
+          <t>2031-10-19</t>
         </is>
       </c>
       <c r="AK54" s="3" t="inlineStr">
@@ -12037,42 +12307,42 @@
       </c>
       <c r="AN54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AV54" s="3" t="inlineStr">
@@ -12100,66 +12370,66 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26常熟经开PPN001</t>
+          <t>26水投债</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>10-15 18:00</t>
-        </is>
-      </c>
-      <c r="C55" s="3"/>
+          <t>10-15 17:00</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>284293.SH</t>
+        </is>
+      </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5.0</v>
+        <v>3.5</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26常经01</t>
+          <t>24黔铁投MTN001</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>4.82Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.8382</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>常熟经开控股有限公司</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="inlineStr">
-        <is>
-          <t>B- 44.89</t>
-        </is>
-      </c>
+          <t>贵州省水利投资(集团)有限责任公司</t>
+        </is>
+      </c>
+      <c r="P55" s="3"/>
       <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -12167,7 +12437,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>10-15 09:00</t>
+          <t>10-15 15:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12196,23 +12466,23 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行定向工具5亿元,本期债务融资工具募集资金拟用于偿还接续“23常熟经开PPN001”的专项过桥贷款[23常熟经开PPN001]</t>
+          <t>本期债券募集资金扣除发行费用后拟全部用于置换发行人已用于偿还公司债券本金的自有资金[23水投03]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司,中国光大银行股份有限公司,宁波银行股份有限公司</t>
+          <t>华创证券有限责任公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF55" s="3" t="inlineStr">
@@ -12222,12 +12492,12 @@
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>常熟经开控股有限公司2026年度第一期定向债务融资工具</t>
+          <t>贵州省水利投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12243,12 +12513,12 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AM55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AN55" s="3" t="inlineStr">
@@ -12258,7 +12528,7 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
@@ -12273,22 +12543,22 @@
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AV55" s="3" t="inlineStr">
@@ -12298,7 +12568,7 @@
       </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX55" s="3" t="inlineStr">
@@ -12316,128 +12586,142 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>华纬转债</t>
+          <t>26安建Y1</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>10-15 15:00</t>
+          <t>10-15 18:00</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>127118.SZ</t>
+          <t>246203.SH</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>5.75</v>
+        <v>5.0</v>
       </c>
       <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 3.20</t>
+        </is>
+      </c>
+      <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>25建工建投MTN001</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>2.06Y</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>2.2961</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>安徽建工建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>D- 3.00</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>10-15 16:00</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>华纬科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="R56" s="3" t="inlineStr">
-        <is>
-          <t>10-15 09:15</t>
-        </is>
-      </c>
-      <c r="S56" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X56" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>2.06%~2.16%</t>
+        </is>
+      </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z56" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>公司本次向不特定对象发行可转换公司债券募集资金总额不超过57,500.00万元(含本数),扣除发行费用后将全部用于以下项目:</t>
+          <t>本期债券募集资金扣除发行费用后拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF56" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG56" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>2026年华纬科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>安徽建工建设投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -12447,7 +12731,7 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2032-10-15</t>
+          <t>2028-10-19</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
@@ -12458,7 +12742,7 @@
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
@@ -12471,25 +12755,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP56" s="3"/>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>交运设备制造</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>道路运输设备</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>零部件</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -12504,7 +12792,7 @@
       </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX56" s="3" t="inlineStr">
@@ -12522,7 +12810,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>G风电K1</t>
+          <t>26仁怀酱酒PPN002</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -12530,45 +12818,41 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>246218.SH</t>
-        </is>
-      </c>
+      <c r="C57" s="3"/>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>3.50 ~ 4.00</t>
         </is>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>25风电K2</t>
+          <t>25仁怀酱酒PPN002</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>3.56Y</t>
+          <t>4.08Y+5.00Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.7091</t>
+          <t>3.1266</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -12578,12 +12862,12 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>中节能风力发电股份有限公司</t>
+          <t>仁怀酱酒(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -12593,7 +12877,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>10-15 16:00</t>
+          <t>10-15 09:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -12603,77 +12887,77 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="U57" s="3"/>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X57" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>2.89%~2.99%</t>
+        </is>
+      </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>贵州省-遵义市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟用于置换12个月内绿色项目相关的自有资金支出。</t>
+          <t>本期定向债务融资工具发行金额1.00亿元,募集资金扣除发行费用后,用于归还发行人到期债务融资工具[25仁怀酱酒PPN001(乡村振兴)]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>贵阳银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>中节能风力发电股份有限公司2026年面向专业投资者公开发行绿色科技创新公司债券(气候主题)(第一期)(品种一)</t>
+          <t>仁怀酱酒(集团)有限责任公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK57" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-10-16</t>
+        </is>
+      </c>
+      <c r="AK57" s="3"/>
       <c r="AL57" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AM57" s="3" t="inlineStr">
@@ -12683,42 +12967,42 @@
       </c>
       <c r="AN57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>饮料制造</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
@@ -12799,7 +13083,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -12835,7 +13119,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X58" s="3"/>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>1.95%~2.05%</t>
+        </is>
+      </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13245,7 +13533,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -13697,7 +13985,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -13737,7 +14025,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X62" s="3"/>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13921,7 +14213,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
@@ -13961,7 +14253,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X63" s="3"/>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>1.45%~1.55%</t>
+        </is>
+      </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -14185,7 +14481,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X64" s="3"/>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.92%</t>
+        </is>
+      </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -14373,7 +14673,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.7000</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
@@ -14413,7 +14713,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X65" s="3"/>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y65" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -14637,7 +14941,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X66" s="3"/>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>2.08%~2.18%</t>
+        </is>
+      </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -14782,7 +15090,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C67" s="3"/>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>102684038.IB</t>
+        </is>
+      </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -14821,7 +15133,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>1.6200/1.6000</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -14861,7 +15173,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X67" s="3"/>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -14998,7 +15314,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C68" s="3"/>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>042680344.IB</t>
+        </is>
+      </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -15037,7 +15357,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/1.5300</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -15077,7 +15397,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X68" s="3"/>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>1.54%~1.58%</t>
+        </is>
+      </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -15205,7 +15529,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ68" s="3"/>
+      <c r="AZ68" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
@@ -15218,7 +15544,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C69" s="3"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>012682447.IB</t>
+        </is>
+      </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -15257,7 +15587,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
@@ -15297,7 +15627,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X69" s="3"/>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>1.46%~1.50%</t>
+        </is>
+      </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -15434,7 +15768,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C70" s="3"/>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>012682445.IB</t>
+        </is>
+      </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -15513,7 +15851,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X70" s="3"/>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>1.94%~1.98%</t>
+        </is>
+      </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -15650,7 +15992,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C71" s="3"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>102684046.IB</t>
+        </is>
+      </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -15689,7 +16035,7 @@
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
@@ -15729,7 +16075,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X71" s="3"/>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -15872,7 +16222,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C72" s="3"/>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>102684019.IB</t>
+        </is>
+      </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -15911,7 +16265,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5700/1.5700</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -15951,7 +16305,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X72" s="3"/>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.61%</t>
+        </is>
+      </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -16088,7 +16446,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C73" s="3"/>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>102684020.IB</t>
+        </is>
+      </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -16127,7 +16489,7 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5700/1.5700</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
@@ -16167,7 +16529,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X73" s="3"/>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.61%</t>
+        </is>
+      </c>
       <c r="Y73" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -16304,7 +16670,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C74" s="3"/>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>102684030.IB</t>
+        </is>
+      </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -16343,7 +16713,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9300/--</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
@@ -16383,7 +16753,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X74" s="3"/>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -16507,7 +16881,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ74" s="3"/>
+      <c r="AZ74" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
@@ -16520,7 +16896,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C75" s="3"/>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>102684031.IB</t>
+        </is>
+      </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -16599,7 +16979,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X75" s="3"/>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y75" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -16740,7 +17124,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C76" s="3"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>102684032.IB</t>
+        </is>
+      </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -16779,7 +17167,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8100/--</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -16819,7 +17207,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X76" s="3"/>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y76" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -16960,7 +17352,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C77" s="3"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>102684043.IB</t>
+        </is>
+      </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -16999,7 +17395,7 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
@@ -17039,7 +17435,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X77" s="3"/>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17176,7 +17576,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C78" s="3"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>042680345.IB</t>
+        </is>
+      </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -17215,7 +17619,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -17255,7 +17659,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X78" s="3"/>
+      <c r="X78" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.55%</t>
+        </is>
+      </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17396,7 +17804,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C79" s="3"/>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>102684022.IB</t>
+        </is>
+      </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -17475,7 +17887,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X79" s="3"/>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y79" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -17612,7 +18028,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C80" s="3"/>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>102684026.IB</t>
+        </is>
+      </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -17651,7 +18071,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/1.6300</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -17691,7 +18111,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X80" s="3"/>
+      <c r="X80" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y80" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17830,7 +18254,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C81" s="3"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>102684041.IB</t>
+        </is>
+      </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -17869,7 +18297,7 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.7000</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
@@ -17909,7 +18337,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X81" s="3"/>
+      <c r="X81" s="3" t="inlineStr">
+        <is>
+          <t>2.58%~2.68%</t>
+        </is>
+      </c>
       <c r="Y81" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -18046,7 +18478,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C82" s="3"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>102684050.IB</t>
+        </is>
+      </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -18125,7 +18561,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X82" s="3"/>
+      <c r="X82" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -18264,7 +18704,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C83" s="3"/>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>102684028.IB</t>
+        </is>
+      </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -18303,7 +18747,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/1.5900</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -18339,7 +18783,11 @@
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
       <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
+      <c r="X83" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y83" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -18476,7 +18924,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C84" s="3"/>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>102684040.IB</t>
+        </is>
+      </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -18555,7 +19007,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X84" s="3"/>
+      <c r="X84" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -18683,7 +19139,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ84" s="3"/>
+      <c r="AZ84" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
@@ -18696,7 +19154,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C85" s="3"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>102684053.IB</t>
+        </is>
+      </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -18735,7 +19197,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/1.6500</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
@@ -18775,7 +19237,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X85" s="3"/>
+      <c r="X85" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -18912,7 +19378,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C86" s="3"/>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>102684016.IB</t>
+        </is>
+      </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -18991,7 +19461,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X86" s="3"/>
+      <c r="X86" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -19128,7 +19602,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C87" s="3"/>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>102684048.IB</t>
+        </is>
+      </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -19167,7 +19645,7 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
@@ -19207,7 +19685,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X87" s="3"/>
+      <c r="X87" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y87" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -19344,7 +19826,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C88" s="3"/>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>102684047.IB</t>
+        </is>
+      </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -19383,7 +19869,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -19423,7 +19909,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X88" s="3"/>
+      <c r="X88" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y88" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -19547,7 +20037,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ88" s="3"/>
+      <c r="AZ88" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
@@ -19560,7 +20052,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C89" s="3"/>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>102690070.IB</t>
+        </is>
+      </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -19599,7 +20095,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/1.7300</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
@@ -19639,7 +20135,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X89" s="3"/>
+      <c r="X89" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y89" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -19780,7 +20280,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C90" s="3"/>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>102684027.IB</t>
+        </is>
+      </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -19859,7 +20363,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X90" s="3"/>
+      <c r="X90" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y90" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -19983,7 +20491,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ90" s="3"/>
+      <c r="AZ90" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="91" customHeight="true" ht="18.0">
       <c r="A91" s="3" t="inlineStr">
@@ -19996,7 +20506,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C91" s="3"/>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>102684042.IB</t>
+        </is>
+      </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -20035,7 +20549,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -20075,7 +20589,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X91" s="3"/>
+      <c r="X91" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y91" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -20212,7 +20730,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C92" s="3"/>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>102684051.IB</t>
+        </is>
+      </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -20251,7 +20773,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6600</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -20291,7 +20813,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X92" s="3"/>
+      <c r="X92" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y92" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -20428,7 +20954,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C93" s="3"/>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>102684017.IB</t>
+        </is>
+      </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -20467,7 +20997,7 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/1.4800</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
@@ -20507,7 +21037,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X93" s="3"/>
+      <c r="X93" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y93" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -20648,7 +21182,11 @@
           <t>10-16 18:00</t>
         </is>
       </c>
-      <c r="C94" s="3"/>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>102684054.IB</t>
+        </is>
+      </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -20687,7 +21225,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9500/--</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -20727,7 +21265,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X94" s="3"/>
+      <c r="X94" s="3" t="inlineStr">
+        <is>
+          <t>1.87%~1.97%</t>
+        </is>
+      </c>
       <c r="Y94" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -20868,7 +21410,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C95" s="3"/>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>102684018.IB</t>
+        </is>
+      </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -20907,7 +21453,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7800</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -20947,7 +21493,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X95" s="3"/>
+      <c r="X95" s="3" t="inlineStr">
+        <is>
+          <t>1.88%~1.98%</t>
+        </is>
+      </c>
       <c r="Y95" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -21171,7 +21721,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X96" s="3"/>
+      <c r="X96" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
       <c r="Y96" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -21312,7 +21866,11 @@
           <t>10-15 18:00</t>
         </is>
       </c>
-      <c r="C97" s="3"/>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>102684024.IB</t>
+        </is>
+      </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -21391,7 +21949,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X97" s="3"/>
+      <c r="X97" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y97" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -21571,7 +22133,7 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -21611,7 +22173,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X98" s="3"/>
+      <c r="X98" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.66%</t>
+        </is>
+      </c>
       <c r="Y98" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -21791,7 +22357,7 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
@@ -21831,7 +22397,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X99" s="3"/>
+      <c r="X99" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y99" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -22055,7 +22625,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X100" s="3"/>
+      <c r="X100" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y100" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -22239,7 +22813,7 @@
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O101" s="3" t="inlineStr">
@@ -22279,7 +22853,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X101" s="3"/>
+      <c r="X101" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y101" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -22463,7 +23041,7 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O102" s="3" t="inlineStr">
@@ -22503,7 +23081,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X102" s="3"/>
+      <c r="X102" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y102" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -22683,7 +23265,7 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
@@ -22723,7 +23305,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X103" s="3"/>
+      <c r="X103" s="3" t="inlineStr">
+        <is>
+          <t>1.69%~1.79%</t>
+        </is>
+      </c>
       <c r="Y103" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -22903,7 +23489,7 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr">
@@ -22943,7 +23529,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X104" s="3"/>
+      <c r="X104" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y104" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -23123,7 +23713,7 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>1.8800/--</t>
+          <t>1.8400/1.8150</t>
         </is>
       </c>
       <c r="O105" s="3" t="inlineStr">
@@ -23163,7 +23753,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X105" s="3"/>
+      <c r="X105" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y105" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -23347,7 +23941,7 @@
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>3.2500/3.1800</t>
         </is>
       </c>
       <c r="O106" s="3" t="inlineStr">
@@ -23387,7 +23981,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X106" s="3"/>
+      <c r="X106" s="3" t="inlineStr">
+        <is>
+          <t>2.92%~3.02%</t>
+        </is>
+      </c>
       <c r="Y106" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -23603,7 +24201,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X107" s="3"/>
+      <c r="X107" s="3" t="inlineStr">
+        <is>
+          <t>1.93%~2.03%</t>
+        </is>
+      </c>
       <c r="Y107" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -23827,7 +24429,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X108" s="3"/>
+      <c r="X108" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y108" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -24047,7 +24653,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X109" s="3"/>
+      <c r="X109" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y109" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -24227,7 +24837,7 @@
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6750/1.6650</t>
         </is>
       </c>
       <c r="O110" s="3" t="inlineStr">
@@ -24267,7 +24877,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X110" s="3"/>
+      <c r="X110" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y110" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -24447,7 +25061,7 @@
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/1.6100</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr">
@@ -24487,7 +25101,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X111" s="3"/>
+      <c r="X111" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y111" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -24611,7 +25229,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ111" s="3"/>
+      <c r="AZ111" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="112" customHeight="true" ht="18.0">
       <c r="A112" s="3" t="inlineStr">
@@ -24707,7 +25327,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X112" s="3"/>
+      <c r="X112" s="3" t="inlineStr">
+        <is>
+          <t>2.27%~2.37%</t>
+        </is>
+      </c>
       <c r="Y112" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -24931,7 +25555,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X113" s="3"/>
+      <c r="X113" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y113" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -25115,7 +25743,7 @@
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O114" s="3" t="inlineStr">
@@ -25155,7 +25783,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X114" s="3"/>
+      <c r="X114" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y114" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -25284,7 +25916,7 @@
     <row r="115" customHeight="true" ht="18.0">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>G风电K2</t>
+          <t>26南控02</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -25294,7 +25926,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>246219.SH</t>
+          <t>246208.SH</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -25315,37 +25947,37 @@
       <c r="I115" s="3"/>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>25风电K2</t>
+          <t>26南海控股MTN004</t>
         </is>
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>3.56Y</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>1.7091</t>
+          <t>1.7255</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>中节能风力发电股份有限公司</t>
+          <t>广东南海控股集团有限公司</t>
         </is>
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>C+ 31.92</t>
         </is>
       </c>
       <c r="Q115" s="3" t="inlineStr">
@@ -25372,7 +26004,7 @@
       <c r="V115" s="3"/>
       <c r="W115" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X115" s="3"/>
@@ -25384,17 +26016,17 @@
       <c r="Z115" s="3"/>
       <c r="AA115" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB115" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟用于置换12个月内绿色项目相关的自有资金支出。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将4.16亿元用于偿还有息债务,剩余部分募集资金用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC115" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD115" s="3"/>
@@ -25405,105 +26037,773 @@
       </c>
       <c r="AF115" s="3" t="inlineStr">
         <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG115" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH115" s="3" t="inlineStr">
+        <is>
+          <t>广东南海控股集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI115" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ115" s="3" t="inlineStr">
+        <is>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK115" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL115" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AO115" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP115" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ115" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR115" s="3" t="inlineStr">
+        <is>
+          <t>综合公用</t>
+        </is>
+      </c>
+      <c r="AS115" s="3" t="inlineStr">
+        <is>
+          <t>综合公用</t>
+        </is>
+      </c>
+      <c r="AT115" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AU115" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV115" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW115" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX115" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AZ115" s="3"/>
+    </row>
+    <row r="116" customHeight="true" ht="18.0">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>26华能山东SCP003</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>10-15 18:00</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>012682451.IB</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>0.25Y</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>25华能山东MTN001</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>2.02Y</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>1.6024</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O116" s="3" t="inlineStr">
+        <is>
+          <t>华能山东发电有限公司</t>
+        </is>
+      </c>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>C 30.00</t>
+        </is>
+      </c>
+      <c r="Q116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="R116" s="3" t="inlineStr">
+        <is>
+          <t>10-15 14:00</t>
+        </is>
+      </c>
+      <c r="S116" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="U116" s="3"/>
+      <c r="V116" s="3"/>
+      <c r="W116" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X116" s="3" t="inlineStr">
+        <is>
+          <t>1.45%~1.49%</t>
+        </is>
+      </c>
+      <c r="Y116" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z116" s="3"/>
+      <c r="AA116" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AB116" s="3" t="inlineStr">
+        <is>
+          <t>本期超短期融资券基础发行金额为0亿元,发行金额上限为10亿元,拟将全部募集资金用于偿还发行人及其下属子公司有息债务。</t>
+        </is>
+      </c>
+      <c r="AC116" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD116" s="3"/>
+      <c r="AE116" s="3" t="inlineStr">
+        <is>
+          <t>超短期融资券(SCP)</t>
+        </is>
+      </c>
+      <c r="AF116" s="3" t="inlineStr">
+        <is>
           <t>国有企业</t>
         </is>
       </c>
-      <c r="AG115" s="3" t="inlineStr">
+      <c r="AG116" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH116" s="3" t="inlineStr">
+        <is>
+          <t>华能山东发电有限公司2026年度第三期超短期融资券</t>
+        </is>
+      </c>
+      <c r="AI116" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ116" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="AK116" s="3"/>
+      <c r="AL116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AM116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AN116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AO116" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP116" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ116" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR116" s="3" t="inlineStr">
+        <is>
+          <t>综合公用</t>
+        </is>
+      </c>
+      <c r="AS116" s="3" t="inlineStr">
+        <is>
+          <t>综合公用</t>
+        </is>
+      </c>
+      <c r="AT116" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU116" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV116" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW116" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX116" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AZ116" s="3"/>
+    </row>
+    <row r="117" customHeight="true" ht="18.0">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>G风电K2</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>10-15 18:00</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>246219.SH</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>25风电K2</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>3.56Y</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>1.7091</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
+          <t>1.7200/--</t>
+        </is>
+      </c>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>中节能风力发电股份有限公司</t>
+        </is>
+      </c>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>C- 20.00</t>
+        </is>
+      </c>
+      <c r="Q117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="R117" s="3" t="inlineStr">
+        <is>
+          <t>10-15 16:00</t>
+        </is>
+      </c>
+      <c r="S117" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="U117" s="3"/>
+      <c r="V117" s="3"/>
+      <c r="W117" s="3" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X117" s="3"/>
+      <c r="Y117" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z117" s="3"/>
+      <c r="AA117" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB117" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后，拟用于置换12个月内绿色项目相关的自有资金支出。</t>
+        </is>
+      </c>
+      <c r="AC117" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD117" s="3"/>
+      <c r="AE117" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF117" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AG117" s="3" t="inlineStr">
         <is>
           <t>上交所</t>
         </is>
       </c>
-      <c r="AH115" s="3" t="inlineStr">
+      <c r="AH117" s="3" t="inlineStr">
         <is>
           <t>中节能风力发电股份有限公司2026年面向专业投资者公开发行绿色科技创新公司债券(气候主题)(第一期)(品种二)</t>
         </is>
       </c>
-      <c r="AI115" s="3" t="inlineStr">
+      <c r="AI117" s="3" t="inlineStr">
         <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="AJ115" s="3" t="inlineStr">
+      <c r="AJ117" s="3" t="inlineStr">
         <is>
           <t>2031-10-19</t>
         </is>
       </c>
-      <c r="AK115" s="3" t="inlineStr">
+      <c r="AK117" s="3" t="inlineStr">
         <is>
           <t>休1</t>
         </is>
       </c>
-      <c r="AL115" s="3" t="inlineStr">
+      <c r="AL117" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AM115" s="3" t="inlineStr">
+      <c r="AM117" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="AN115" s="3" t="inlineStr">
+      <c r="AN117" s="3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AO115" s="3" t="inlineStr">
+      <c r="AO117" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP115" s="3" t="inlineStr">
+      <c r="AP117" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AQ115" s="3" t="inlineStr">
+      <c r="AQ117" s="3" t="inlineStr">
         <is>
           <t>公用事业</t>
         </is>
       </c>
-      <c r="AR115" s="3" t="inlineStr">
+      <c r="AR117" s="3" t="inlineStr">
         <is>
           <t>电力</t>
         </is>
       </c>
-      <c r="AS115" s="3" t="inlineStr">
+      <c r="AS117" s="3" t="inlineStr">
         <is>
           <t>风电</t>
         </is>
       </c>
-      <c r="AT115" s="3" t="inlineStr">
+      <c r="AT117" s="3" t="inlineStr">
         <is>
           <t>电力</t>
         </is>
       </c>
-      <c r="AU115" s="3" t="inlineStr">
+      <c r="AU117" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AV115" s="3" t="inlineStr">
+      <c r="AV117" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AW115" s="3" t="inlineStr">
+      <c r="AW117" s="3" t="inlineStr">
         <is>
           <t>不含权</t>
         </is>
       </c>
-      <c r="AX115" s="3" t="inlineStr">
+      <c r="AX117" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY115" s="3" t="inlineStr">
+      <c r="AY117" s="3" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ115" s="3"/>
+      <c r="AZ117" s="3"/>
+    </row>
+    <row r="118" customHeight="true" ht="18.0">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>26溧水03</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>10-15 18:00</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>284247.SH</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>26溧水02</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>4.88Y</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>1.8207</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>1.8300/1.7900</t>
+        </is>
+      </c>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>南京溧水城市建设集团有限公司</t>
+        </is>
+      </c>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>C 25.20</t>
+        </is>
+      </c>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="R118" s="3" t="inlineStr">
+        <is>
+          <t>10-15 15:00</t>
+        </is>
+      </c>
+      <c r="S118" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="U118" s="3"/>
+      <c r="V118" s="3"/>
+      <c r="W118" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X118" s="3"/>
+      <c r="Y118" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z118" s="3"/>
+      <c r="AA118" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-南京市</t>
+        </is>
+      </c>
+      <c r="AB118" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券本金。[23溧水F3]</t>
+        </is>
+      </c>
+      <c r="AC118" s="3" t="inlineStr">
+        <is>
+          <t>东吴证券股份有限公司,国金证券股份有限公司,天风证券股份有限公司,华安证券股份有限公司,长城证券股份有限公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD118" s="3"/>
+      <c r="AE118" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF118" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG118" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH118" s="3" t="inlineStr">
+        <is>
+          <t>南京溧水城市建设集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="AI118" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ118" s="3" t="inlineStr">
+        <is>
+          <t>2031-10-16</t>
+        </is>
+      </c>
+      <c r="AK118" s="3"/>
+      <c r="AL118" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AO118" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP118" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ118" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR118" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS118" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT118" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU118" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV118" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW118" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX118" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AZ118" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
